--- a/Team-Data/2011-12/4-18-2011-12.xlsx
+++ b/Team-Data/2011-12/4-18-2011-12.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,67 +728,67 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F2" t="n">
         <v>25</v>
       </c>
       <c r="G2" t="n">
-        <v>0.597</v>
+        <v>0.59</v>
       </c>
       <c r="H2" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="I2" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J2" t="n">
-        <v>81.09999999999999</v>
+        <v>81</v>
       </c>
       <c r="K2" t="n">
-        <v>0.45</v>
+        <v>0.449</v>
       </c>
       <c r="L2" t="n">
         <v>7.2</v>
       </c>
       <c r="M2" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="N2" t="n">
-        <v>0.362</v>
+        <v>0.363</v>
       </c>
       <c r="O2" t="n">
-        <v>15.8</v>
+        <v>15.6</v>
       </c>
       <c r="P2" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.739</v>
+        <v>0.737</v>
       </c>
       <c r="R2" t="n">
         <v>10</v>
       </c>
       <c r="S2" t="n">
-        <v>31.4</v>
+        <v>31.1</v>
       </c>
       <c r="T2" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="U2" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="V2" t="n">
-        <v>13.7</v>
+        <v>13.9</v>
       </c>
       <c r="W2" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y2" t="n">
         <v>4.9</v>
@@ -733,13 +800,13 @@
         <v>19.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>96</v>
+        <v>95.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE2" t="n">
         <v>8</v>
@@ -766,25 +833,25 @@
         <v>9</v>
       </c>
       <c r="AM2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AO2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AP2" t="n">
         <v>23</v>
       </c>
       <c r="AQ2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR2" t="n">
         <v>28</v>
       </c>
       <c r="AS2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AT2" t="n">
         <v>23</v>
@@ -796,7 +863,7 @@
         <v>4</v>
       </c>
       <c r="AW2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX2" t="n">
         <v>23</v>
@@ -814,7 +881,7 @@
         <v>18</v>
       </c>
       <c r="BC2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-18-2011-12</t>
+          <t>2012-04-18</t>
         </is>
       </c>
     </row>
@@ -843,55 +910,55 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E3" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F3" t="n">
         <v>26</v>
       </c>
       <c r="G3" t="n">
-        <v>0.587</v>
+        <v>0.581</v>
       </c>
       <c r="H3" t="n">
         <v>48.3</v>
       </c>
       <c r="I3" t="n">
-        <v>35.5</v>
+        <v>35.4</v>
       </c>
       <c r="J3" t="n">
-        <v>76.90000000000001</v>
+        <v>77</v>
       </c>
       <c r="K3" t="n">
-        <v>0.461</v>
+        <v>0.46</v>
       </c>
       <c r="L3" t="n">
         <v>5.5</v>
       </c>
       <c r="M3" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="N3" t="n">
         <v>0.368</v>
       </c>
       <c r="O3" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="P3" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.781</v>
+        <v>0.779</v>
       </c>
       <c r="R3" t="n">
         <v>7.8</v>
       </c>
       <c r="S3" t="n">
-        <v>31</v>
+        <v>31.1</v>
       </c>
       <c r="T3" t="n">
-        <v>38.8</v>
+        <v>39</v>
       </c>
       <c r="U3" t="n">
         <v>23.8</v>
@@ -912,31 +979,31 @@
         <v>20.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>92.09999999999999</v>
+        <v>92</v>
       </c>
       <c r="AC3" t="n">
         <v>2.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE3" t="n">
         <v>8</v>
       </c>
       <c r="AF3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH3" t="n">
         <v>20</v>
       </c>
       <c r="AI3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ3" t="n">
         <v>30</v>
@@ -954,7 +1021,7 @@
         <v>6</v>
       </c>
       <c r="AO3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AP3" t="n">
         <v>26</v>
@@ -972,25 +1039,25 @@
         <v>30</v>
       </c>
       <c r="AU3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV3" t="n">
         <v>18</v>
       </c>
       <c r="AW3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ3" t="n">
         <v>20</v>
       </c>
       <c r="BA3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB3" t="n">
         <v>26</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-18-2011-12</t>
+          <t>2012-04-18</t>
         </is>
       </c>
     </row>
@@ -1025,37 +1092,37 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E4" t="n">
         <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G4" t="n">
-        <v>0.115</v>
+        <v>0.117</v>
       </c>
       <c r="H4" t="n">
         <v>48.2</v>
       </c>
       <c r="I4" t="n">
-        <v>33.3</v>
+        <v>33.5</v>
       </c>
       <c r="J4" t="n">
-        <v>80.5</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.414</v>
+        <v>0.416</v>
       </c>
       <c r="L4" t="n">
         <v>4</v>
       </c>
       <c r="M4" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0.296</v>
+        <v>0.298</v>
       </c>
       <c r="O4" t="n">
         <v>16.5</v>
@@ -1067,19 +1134,19 @@
         <v>0.747</v>
       </c>
       <c r="R4" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="S4" t="n">
-        <v>28.7</v>
+        <v>28.8</v>
       </c>
       <c r="T4" t="n">
         <v>39</v>
       </c>
       <c r="U4" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="V4" t="n">
-        <v>14.1</v>
+        <v>14.3</v>
       </c>
       <c r="W4" t="n">
         <v>6.2</v>
@@ -1094,13 +1161,13 @@
         <v>19.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>87.2</v>
+        <v>87.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>-13.6</v>
+        <v>-13.3</v>
       </c>
       <c r="AD4" t="n">
         <v>25</v>
@@ -1127,10 +1194,10 @@
         <v>30</v>
       </c>
       <c r="AL4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AN4" t="n">
         <v>30</v>
@@ -1154,10 +1221,10 @@
         <v>29</v>
       </c>
       <c r="AU4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AW4" t="n">
         <v>29</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-18-2011-12</t>
+          <t>2012-04-18</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E5" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F5" t="n">
         <v>15</v>
       </c>
       <c r="G5" t="n">
-        <v>0.758</v>
+        <v>0.754</v>
       </c>
       <c r="H5" t="n">
         <v>48.3</v>
@@ -1237,34 +1304,34 @@
         <v>16.9</v>
       </c>
       <c r="N5" t="n">
-        <v>0.379</v>
+        <v>0.377</v>
       </c>
       <c r="O5" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="P5" t="n">
         <v>21.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.72</v>
+        <v>0.722</v>
       </c>
       <c r="R5" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="V5" t="n">
         <v>14.2</v>
       </c>
-      <c r="S5" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="T5" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="U5" t="n">
-        <v>23</v>
-      </c>
-      <c r="V5" t="n">
-        <v>14.1</v>
-      </c>
       <c r="W5" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X5" t="n">
         <v>6</v>
@@ -1279,13 +1346,13 @@
         <v>18</v>
       </c>
       <c r="AB5" t="n">
-        <v>96.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1315,10 +1382,10 @@
         <v>19</v>
       </c>
       <c r="AN5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP5" t="n">
         <v>20</v>
@@ -1330,7 +1397,7 @@
         <v>1</v>
       </c>
       <c r="AS5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT5" t="n">
         <v>1</v>
@@ -1339,7 +1406,7 @@
         <v>4</v>
       </c>
       <c r="AV5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW5" t="n">
         <v>24</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-18-2011-12</t>
+          <t>2012-04-18</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E6" t="n">
         <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
-        <v>0.328</v>
+        <v>0.333</v>
       </c>
       <c r="H6" t="n">
         <v>48.4</v>
@@ -1407,7 +1474,7 @@
         <v>34.2</v>
       </c>
       <c r="J6" t="n">
-        <v>81.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="K6" t="n">
         <v>0.422</v>
@@ -1416,28 +1483,28 @@
         <v>6.8</v>
       </c>
       <c r="M6" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="N6" t="n">
         <v>0.35</v>
       </c>
       <c r="O6" t="n">
-        <v>17.9</v>
+        <v>18.1</v>
       </c>
       <c r="P6" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.717</v>
+        <v>0.718</v>
       </c>
       <c r="R6" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="S6" t="n">
         <v>29.6</v>
       </c>
       <c r="T6" t="n">
-        <v>42.3</v>
+        <v>42.5</v>
       </c>
       <c r="U6" t="n">
         <v>20.2</v>
@@ -1446,25 +1513,25 @@
         <v>15.5</v>
       </c>
       <c r="W6" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X6" t="n">
         <v>4</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>93.2</v>
+        <v>93.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>-6.8</v>
+        <v>-6.7</v>
       </c>
       <c r="AD6" t="n">
         <v>25</v>
@@ -1497,13 +1564,13 @@
         <v>17</v>
       </c>
       <c r="AN6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO6" t="n">
         <v>9</v>
       </c>
       <c r="AP6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ6" t="n">
         <v>28</v>
@@ -1512,16 +1579,16 @@
         <v>4</v>
       </c>
       <c r="AS6" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AT6" t="n">
         <v>13</v>
       </c>
       <c r="AU6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW6" t="n">
         <v>22</v>
@@ -1533,13 +1600,13 @@
         <v>28</v>
       </c>
       <c r="AZ6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BA6" t="n">
         <v>6</v>
       </c>
       <c r="BB6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BC6" t="n">
         <v>29</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-18-2011-12</t>
+          <t>2012-04-18</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E7" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F7" t="n">
         <v>28</v>
       </c>
       <c r="G7" t="n">
-        <v>0.556</v>
+        <v>0.548</v>
       </c>
       <c r="H7" t="n">
         <v>48.7</v>
@@ -1589,34 +1656,34 @@
         <v>36.4</v>
       </c>
       <c r="J7" t="n">
-        <v>82.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0.444</v>
+        <v>0.443</v>
       </c>
       <c r="L7" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="M7" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="N7" t="n">
-        <v>0.343</v>
+        <v>0.341</v>
       </c>
       <c r="O7" t="n">
-        <v>15.4</v>
+        <v>15.2</v>
       </c>
       <c r="P7" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.765</v>
+        <v>0.762</v>
       </c>
       <c r="R7" t="n">
         <v>10</v>
       </c>
       <c r="S7" t="n">
-        <v>32.6</v>
+        <v>32.7</v>
       </c>
       <c r="T7" t="n">
         <v>42.7</v>
@@ -1634,7 +1701,7 @@
         <v>5.2</v>
       </c>
       <c r="Y7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Z7" t="n">
         <v>18.8</v>
@@ -1643,22 +1710,22 @@
         <v>18.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>96</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE7" t="n">
         <v>12</v>
       </c>
       <c r="AF7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH7" t="n">
         <v>3</v>
@@ -1670,7 +1737,7 @@
         <v>13</v>
       </c>
       <c r="AK7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL7" t="n">
         <v>6</v>
@@ -1679,13 +1746,13 @@
         <v>4</v>
       </c>
       <c r="AN7" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AO7" t="n">
         <v>27</v>
       </c>
       <c r="AP7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ7" t="n">
         <v>12</v>
@@ -1694,10 +1761,10 @@
         <v>27</v>
       </c>
       <c r="AS7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU7" t="n">
         <v>14</v>
@@ -1709,13 +1776,13 @@
         <v>4</v>
       </c>
       <c r="AX7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA7" t="n">
         <v>27</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-18-2011-12</t>
+          <t>2012-04-18</t>
         </is>
       </c>
     </row>
@@ -1753,55 +1820,55 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E8" t="n">
         <v>34</v>
       </c>
       <c r="F8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G8" t="n">
-        <v>0.548</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I8" t="n">
         <v>38.5</v>
       </c>
       <c r="J8" t="n">
-        <v>81.59999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="K8" t="n">
         <v>0.471</v>
       </c>
       <c r="L8" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="M8" t="n">
         <v>20.2</v>
       </c>
       <c r="N8" t="n">
-        <v>0.329</v>
+        <v>0.33</v>
       </c>
       <c r="O8" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="P8" t="n">
         <v>27.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.735</v>
+        <v>0.734</v>
       </c>
       <c r="R8" t="n">
         <v>11.2</v>
       </c>
       <c r="S8" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
       <c r="T8" t="n">
-        <v>43.1</v>
+        <v>43.2</v>
       </c>
       <c r="U8" t="n">
         <v>23.8</v>
@@ -1822,25 +1889,25 @@
         <v>19.7</v>
       </c>
       <c r="AA8" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>103.5</v>
+        <v>103.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AD8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF8" t="n">
         <v>12</v>
       </c>
       <c r="AG8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH8" t="n">
         <v>5</v>
@@ -1861,7 +1928,7 @@
         <v>10</v>
       </c>
       <c r="AN8" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AO8" t="n">
         <v>3</v>
@@ -1882,13 +1949,13 @@
         <v>7</v>
       </c>
       <c r="AU8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX8" t="n">
         <v>15</v>
@@ -1897,7 +1964,7 @@
         <v>30</v>
       </c>
       <c r="AZ8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA8" t="n">
         <v>1</v>
@@ -1906,7 +1973,7 @@
         <v>1</v>
       </c>
       <c r="BC8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-18-2011-12</t>
+          <t>2012-04-18</t>
         </is>
       </c>
     </row>
@@ -1935,64 +2002,64 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E9" t="n">
         <v>23</v>
       </c>
       <c r="F9" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G9" t="n">
-        <v>0.371</v>
+        <v>0.377</v>
       </c>
       <c r="H9" t="n">
         <v>48.4</v>
       </c>
       <c r="I9" t="n">
-        <v>34.7</v>
+        <v>34.8</v>
       </c>
       <c r="J9" t="n">
-        <v>79.09999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.439</v>
+        <v>0.441</v>
       </c>
       <c r="L9" t="n">
         <v>4.6</v>
       </c>
       <c r="M9" t="n">
-        <v>13.5</v>
+        <v>13.3</v>
       </c>
       <c r="N9" t="n">
-        <v>0.343</v>
+        <v>0.345</v>
       </c>
       <c r="O9" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="P9" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.757</v>
+        <v>0.758</v>
       </c>
       <c r="R9" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="S9" t="n">
-        <v>28.4</v>
+        <v>28.2</v>
       </c>
       <c r="T9" t="n">
-        <v>40.1</v>
+        <v>40</v>
       </c>
       <c r="U9" t="n">
         <v>18.7</v>
       </c>
       <c r="V9" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="W9" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X9" t="n">
         <v>4.2</v>
@@ -2004,22 +2071,22 @@
         <v>19.7</v>
       </c>
       <c r="AA9" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>90.90000000000001</v>
+        <v>91</v>
       </c>
       <c r="AC9" t="n">
-        <v>-5.2</v>
+        <v>-4.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE9" t="n">
         <v>22</v>
       </c>
       <c r="AF9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG9" t="n">
         <v>22</v>
@@ -2034,16 +2101,16 @@
         <v>25</v>
       </c>
       <c r="AK9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL9" t="n">
         <v>26</v>
       </c>
       <c r="AM9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AN9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO9" t="n">
         <v>14</v>
@@ -2052,10 +2119,10 @@
         <v>14</v>
       </c>
       <c r="AQ9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS9" t="n">
         <v>30</v>
@@ -2073,7 +2140,7 @@
         <v>23</v>
       </c>
       <c r="AX9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY9" t="n">
         <v>21</v>
@@ -2082,7 +2149,7 @@
         <v>17</v>
       </c>
       <c r="BA9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB9" t="n">
         <v>28</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-18-2011-12</t>
+          <t>2012-04-18</t>
         </is>
       </c>
     </row>
@@ -2117,46 +2184,46 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E10" t="n">
         <v>22</v>
       </c>
       <c r="F10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G10" t="n">
-        <v>0.361</v>
+        <v>0.367</v>
       </c>
       <c r="H10" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="I10" t="n">
         <v>37.7</v>
       </c>
       <c r="J10" t="n">
-        <v>82.40000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="K10" t="n">
         <v>0.457</v>
       </c>
       <c r="L10" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M10" t="n">
         <v>21</v>
       </c>
       <c r="N10" t="n">
-        <v>0.389</v>
+        <v>0.392</v>
       </c>
       <c r="O10" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="P10" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.775</v>
+        <v>0.776</v>
       </c>
       <c r="R10" t="n">
         <v>9.800000000000001</v>
@@ -2186,13 +2253,13 @@
         <v>21.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>16.6</v>
+        <v>16.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>98.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.4</v>
+        <v>-3.3</v>
       </c>
       <c r="AD10" t="n">
         <v>25</v>
@@ -2201,7 +2268,7 @@
         <v>23</v>
       </c>
       <c r="AF10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG10" t="n">
         <v>23</v>
@@ -2213,7 +2280,7 @@
         <v>7</v>
       </c>
       <c r="AJ10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK10" t="n">
         <v>8</v>
@@ -2225,7 +2292,7 @@
         <v>8</v>
       </c>
       <c r="AN10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO10" t="n">
         <v>29</v>
@@ -2234,7 +2301,7 @@
         <v>29</v>
       </c>
       <c r="AQ10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR10" t="n">
         <v>29</v>
@@ -2252,10 +2319,10 @@
         <v>5</v>
       </c>
       <c r="AW10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AY10" t="n">
         <v>13</v>
@@ -2267,7 +2334,7 @@
         <v>29</v>
       </c>
       <c r="BB10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BC10" t="n">
         <v>22</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-18-2011-12</t>
+          <t>2012-04-18</t>
         </is>
       </c>
     </row>
@@ -2299,43 +2366,43 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E11" t="n">
         <v>32</v>
       </c>
       <c r="F11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G11" t="n">
-        <v>0.516</v>
+        <v>0.525</v>
       </c>
       <c r="H11" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I11" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="J11" t="n">
         <v>83.90000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="L11" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="M11" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="N11" t="n">
-        <v>0.36</v>
+        <v>0.358</v>
       </c>
       <c r="O11" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="P11" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="Q11" t="n">
         <v>0.788</v>
@@ -2350,58 +2417,58 @@
         <v>42.1</v>
       </c>
       <c r="U11" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="V11" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W11" t="n">
         <v>7.4</v>
       </c>
       <c r="X11" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>98.5</v>
+        <v>98.3</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE11" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AF11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG11" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH11" t="n">
         <v>5</v>
       </c>
       <c r="AI11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ11" t="n">
         <v>3</v>
       </c>
       <c r="AK11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AL11" t="n">
         <v>12</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>11</v>
       </c>
       <c r="AM11" t="n">
         <v>14</v>
@@ -2410,7 +2477,7 @@
         <v>10</v>
       </c>
       <c r="AO11" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AP11" t="n">
         <v>28</v>
@@ -2425,31 +2492,31 @@
         <v>18</v>
       </c>
       <c r="AT11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU11" t="n">
         <v>12</v>
       </c>
       <c r="AV11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW11" t="n">
         <v>18</v>
       </c>
       <c r="AX11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY11" t="n">
         <v>19</v>
       </c>
       <c r="AZ11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA11" t="n">
         <v>25</v>
       </c>
       <c r="BB11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BC11" t="n">
         <v>17</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-18-2011-12</t>
+          <t>2012-04-18</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>3.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
         <v>5</v>
@@ -2571,10 +2638,10 @@
         <v>5</v>
       </c>
       <c r="AH12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AI12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ12" t="n">
         <v>19</v>
@@ -2613,7 +2680,7 @@
         <v>29</v>
       </c>
       <c r="AV12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AW12" t="n">
         <v>14</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-18-2011-12</t>
+          <t>2012-04-18</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E13" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F13" t="n">
         <v>23</v>
       </c>
       <c r="G13" t="n">
-        <v>0.629</v>
+        <v>0.623</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
@@ -2681,43 +2748,43 @@
         <v>37</v>
       </c>
       <c r="J13" t="n">
-        <v>81.5</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.454</v>
+        <v>0.453</v>
       </c>
       <c r="L13" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="M13" t="n">
         <v>21.8</v>
       </c>
       <c r="N13" t="n">
-        <v>0.357</v>
+        <v>0.353</v>
       </c>
       <c r="O13" t="n">
         <v>15.7</v>
       </c>
       <c r="P13" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="Q13" t="n">
         <v>0.679</v>
       </c>
       <c r="R13" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="S13" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="T13" t="n">
-        <v>41.7</v>
+        <v>41.8</v>
       </c>
       <c r="U13" t="n">
         <v>21.1</v>
       </c>
       <c r="V13" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="W13" t="n">
         <v>8.300000000000001</v>
@@ -2729,19 +2796,19 @@
         <v>4.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AA13" t="n">
         <v>21.3</v>
       </c>
       <c r="AB13" t="n">
-        <v>97.5</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AC13" t="n">
         <v>2.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE13" t="n">
         <v>7</v>
@@ -2771,13 +2838,13 @@
         <v>5</v>
       </c>
       <c r="AN13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP13" t="n">
         <v>11</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>23</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>12</v>
       </c>
       <c r="AQ13" t="n">
         <v>29</v>
@@ -2798,25 +2865,25 @@
         <v>2</v>
       </c>
       <c r="AW13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX13" t="n">
         <v>20</v>
       </c>
       <c r="AY13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ13" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BA13" t="n">
         <v>5</v>
       </c>
       <c r="BB13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-18-2011-12</t>
+          <t>2012-04-18</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E14" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F14" t="n">
         <v>23</v>
       </c>
       <c r="G14" t="n">
-        <v>0.635</v>
+        <v>0.629</v>
       </c>
       <c r="H14" t="n">
         <v>48.6</v>
@@ -2866,22 +2933,22 @@
         <v>80.09999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L14" t="n">
         <v>5.5</v>
       </c>
       <c r="M14" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="N14" t="n">
-        <v>0.322</v>
+        <v>0.324</v>
       </c>
       <c r="O14" t="n">
         <v>18.1</v>
       </c>
       <c r="P14" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="Q14" t="n">
         <v>0.757</v>
@@ -2890,16 +2957,16 @@
         <v>12</v>
       </c>
       <c r="S14" t="n">
-        <v>34.3</v>
+        <v>34.1</v>
       </c>
       <c r="T14" t="n">
-        <v>46.2</v>
+        <v>46.1</v>
       </c>
       <c r="U14" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="V14" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W14" t="n">
         <v>5.8</v>
@@ -2911,22 +2978,22 @@
         <v>4.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="AA14" t="n">
         <v>20.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>97.09999999999999</v>
+        <v>97</v>
       </c>
       <c r="AC14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD14" t="n">
         <v>2</v>
       </c>
-      <c r="AD14" t="n">
-        <v>1</v>
-      </c>
       <c r="AE14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF14" t="n">
         <v>6</v>
@@ -2938,7 +3005,7 @@
         <v>7</v>
       </c>
       <c r="AI14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ14" t="n">
         <v>23</v>
@@ -2962,7 +3029,7 @@
         <v>9</v>
       </c>
       <c r="AQ14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR14" t="n">
         <v>11</v>
@@ -2998,7 +3065,7 @@
         <v>16</v>
       </c>
       <c r="BC14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-18-2011-12</t>
+          <t>2012-04-18</t>
         </is>
       </c>
     </row>
@@ -3027,67 +3094,67 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E15" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F15" t="n">
         <v>25</v>
       </c>
       <c r="G15" t="n">
-        <v>0.597</v>
+        <v>0.59</v>
       </c>
       <c r="H15" t="n">
         <v>48.3</v>
       </c>
       <c r="I15" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J15" t="n">
         <v>82.3</v>
       </c>
       <c r="K15" t="n">
-        <v>0.447</v>
+        <v>0.446</v>
       </c>
       <c r="L15" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="M15" t="n">
-        <v>12.9</v>
+        <v>12.7</v>
       </c>
       <c r="N15" t="n">
-        <v>0.33</v>
+        <v>0.329</v>
       </c>
       <c r="O15" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="P15" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="R15" t="n">
         <v>12.5</v>
       </c>
       <c r="S15" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="T15" t="n">
-        <v>42</v>
+        <v>42.2</v>
       </c>
       <c r="U15" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="V15" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W15" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="X15" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y15" t="n">
         <v>5.6</v>
@@ -3096,16 +3163,16 @@
         <v>19.9</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>95.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE15" t="n">
         <v>8</v>
@@ -3120,13 +3187,13 @@
         <v>15</v>
       </c>
       <c r="AI15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ15" t="n">
         <v>11</v>
       </c>
       <c r="AK15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL15" t="n">
         <v>27</v>
@@ -3135,7 +3202,7 @@
         <v>28</v>
       </c>
       <c r="AN15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO15" t="n">
         <v>10</v>
@@ -3144,16 +3211,16 @@
         <v>13</v>
       </c>
       <c r="AQ15" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AR15" t="n">
         <v>5</v>
       </c>
       <c r="AS15" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AT15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU15" t="n">
         <v>24</v>
@@ -3165,7 +3232,7 @@
         <v>1</v>
       </c>
       <c r="AX15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY15" t="n">
         <v>22</v>
@@ -3180,7 +3247,7 @@
         <v>20</v>
       </c>
       <c r="BC15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-18-2011-12</t>
+          <t>2012-04-18</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E16" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F16" t="n">
         <v>17</v>
       </c>
       <c r="G16" t="n">
-        <v>0.721</v>
+        <v>0.717</v>
       </c>
       <c r="H16" t="n">
         <v>48.7</v>
@@ -3227,10 +3294,10 @@
         <v>37.6</v>
       </c>
       <c r="J16" t="n">
-        <v>79.2</v>
+        <v>79.3</v>
       </c>
       <c r="K16" t="n">
-        <v>0.475</v>
+        <v>0.474</v>
       </c>
       <c r="L16" t="n">
         <v>5.6</v>
@@ -3242,13 +3309,13 @@
         <v>0.363</v>
       </c>
       <c r="O16" t="n">
-        <v>19.1</v>
+        <v>19.3</v>
       </c>
       <c r="P16" t="n">
-        <v>24.7</v>
+        <v>24.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.774</v>
+        <v>0.776</v>
       </c>
       <c r="R16" t="n">
         <v>10.3</v>
@@ -3275,16 +3342,16 @@
         <v>4.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AA16" t="n">
         <v>20.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>100</v>
+        <v>100.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="AD16" t="n">
         <v>25</v>
@@ -3326,7 +3393,7 @@
         <v>8</v>
       </c>
       <c r="AQ16" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AR16" t="n">
         <v>24</v>
@@ -3347,13 +3414,13 @@
         <v>3</v>
       </c>
       <c r="AX16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY16" t="n">
         <v>3</v>
       </c>
       <c r="AZ16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA16" t="n">
         <v>8</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-18-2011-12</t>
+          <t>2012-04-18</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E17" t="n">
         <v>29</v>
       </c>
       <c r="F17" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G17" t="n">
-        <v>0.475</v>
+        <v>0.483</v>
       </c>
       <c r="H17" t="n">
         <v>48.1</v>
@@ -3409,7 +3476,7 @@
         <v>38.2</v>
       </c>
       <c r="J17" t="n">
-        <v>86</v>
+        <v>85.8</v>
       </c>
       <c r="K17" t="n">
         <v>0.445</v>
@@ -3421,31 +3488,31 @@
         <v>19.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0.346</v>
+        <v>0.348</v>
       </c>
       <c r="O17" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="P17" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.776</v>
+        <v>0.774</v>
       </c>
       <c r="R17" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="S17" t="n">
         <v>29.5</v>
       </c>
       <c r="T17" t="n">
-        <v>42</v>
+        <v>41.9</v>
       </c>
       <c r="U17" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="V17" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="W17" t="n">
         <v>8.300000000000001</v>
@@ -3454,19 +3521,19 @@
         <v>5</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z17" t="n">
         <v>19.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>99.5</v>
+        <v>99.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AD17" t="n">
         <v>25</v>
@@ -3508,13 +3575,13 @@
         <v>24</v>
       </c>
       <c r="AQ17" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AR17" t="n">
         <v>6</v>
       </c>
       <c r="AS17" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AT17" t="n">
         <v>17</v>
@@ -3523,13 +3590,13 @@
         <v>1</v>
       </c>
       <c r="AV17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW17" t="n">
         <v>6</v>
       </c>
-      <c r="AW17" t="n">
-        <v>7</v>
-      </c>
       <c r="AX17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY17" t="n">
         <v>6</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-18-2011-12</t>
+          <t>2012-04-18</t>
         </is>
       </c>
     </row>
@@ -3663,13 +3730,13 @@
         <v>21</v>
       </c>
       <c r="AH18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI18" t="n">
         <v>20</v>
       </c>
       <c r="AJ18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK18" t="n">
         <v>26</v>
@@ -3690,25 +3757,25 @@
         <v>4</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR18" t="n">
         <v>8</v>
       </c>
       <c r="AS18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU18" t="n">
         <v>25</v>
       </c>
       <c r="AV18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX18" t="n">
         <v>25</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-18-2011-12</t>
+          <t>2012-04-18</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E19" t="n">
         <v>22</v>
       </c>
       <c r="F19" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G19" t="n">
-        <v>0.349</v>
+        <v>0.355</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
@@ -3773,7 +3840,7 @@
         <v>34.4</v>
       </c>
       <c r="J19" t="n">
-        <v>80.59999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="K19" t="n">
         <v>0.426</v>
@@ -3785,34 +3852,34 @@
         <v>22.8</v>
       </c>
       <c r="N19" t="n">
-        <v>0.343</v>
+        <v>0.342</v>
       </c>
       <c r="O19" t="n">
         <v>17</v>
       </c>
       <c r="P19" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.776</v>
+        <v>0.775</v>
       </c>
       <c r="R19" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S19" t="n">
-        <v>28.4</v>
+        <v>28.3</v>
       </c>
       <c r="T19" t="n">
         <v>40.4</v>
       </c>
       <c r="U19" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="V19" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W19" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X19" t="n">
         <v>4</v>
@@ -3821,19 +3888,19 @@
         <v>5</v>
       </c>
       <c r="Z19" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>93.59999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="AC19" t="n">
         <v>-5.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE19" t="n">
         <v>23</v>
@@ -3863,7 +3930,7 @@
         <v>3</v>
       </c>
       <c r="AN19" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AO19" t="n">
         <v>13</v>
@@ -3872,7 +3939,7 @@
         <v>16</v>
       </c>
       <c r="AQ19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR19" t="n">
         <v>10</v>
@@ -3887,10 +3954,10 @@
         <v>22</v>
       </c>
       <c r="AV19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX19" t="n">
         <v>29</v>
@@ -3902,7 +3969,7 @@
         <v>12</v>
       </c>
       <c r="BA19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB19" t="n">
         <v>22</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-18-2011-12</t>
+          <t>2012-04-18</t>
         </is>
       </c>
     </row>
@@ -3937,61 +4004,61 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E20" t="n">
         <v>19</v>
       </c>
       <c r="F20" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G20" t="n">
-        <v>0.306</v>
+        <v>0.311</v>
       </c>
       <c r="H20" t="n">
         <v>48.2</v>
       </c>
       <c r="I20" t="n">
-        <v>34.9</v>
+        <v>35</v>
       </c>
       <c r="J20" t="n">
-        <v>77.5</v>
+        <v>77.8</v>
       </c>
       <c r="K20" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="L20" t="n">
         <v>4</v>
       </c>
       <c r="M20" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="N20" t="n">
         <v>0.338</v>
       </c>
       <c r="O20" t="n">
-        <v>15.7</v>
+        <v>15.5</v>
       </c>
       <c r="P20" t="n">
-        <v>20.6</v>
+        <v>20.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.764</v>
+        <v>0.762</v>
       </c>
       <c r="R20" t="n">
         <v>11</v>
       </c>
       <c r="S20" t="n">
-        <v>29.9</v>
+        <v>30</v>
       </c>
       <c r="T20" t="n">
-        <v>40.9</v>
+        <v>41</v>
       </c>
       <c r="U20" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="V20" t="n">
-        <v>15.5</v>
+        <v>15.3</v>
       </c>
       <c r="W20" t="n">
         <v>7.3</v>
@@ -4003,19 +4070,19 @@
         <v>5.8</v>
       </c>
       <c r="Z20" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>89.59999999999999</v>
+        <v>89.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>-3.9</v>
+        <v>-3.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE20" t="n">
         <v>28</v>
@@ -4036,7 +4103,7 @@
         <v>29</v>
       </c>
       <c r="AK20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL20" t="n">
         <v>30</v>
@@ -4045,16 +4112,16 @@
         <v>30</v>
       </c>
       <c r="AN20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO20" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AP20" t="n">
         <v>25</v>
       </c>
       <c r="AQ20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR20" t="n">
         <v>19</v>
@@ -4072,7 +4139,7 @@
         <v>25</v>
       </c>
       <c r="AW20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX20" t="n">
         <v>21</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-18-2011-12</t>
+          <t>2012-04-18</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E21" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F21" t="n">
         <v>29</v>
       </c>
       <c r="G21" t="n">
-        <v>0.532</v>
+        <v>0.525</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
@@ -4140,16 +4207,16 @@
         <v>80.8</v>
       </c>
       <c r="K21" t="n">
-        <v>0.44</v>
+        <v>0.441</v>
       </c>
       <c r="L21" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="M21" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="N21" t="n">
-        <v>0.33</v>
+        <v>0.329</v>
       </c>
       <c r="O21" t="n">
         <v>18.7</v>
@@ -4158,7 +4225,7 @@
         <v>25.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.745</v>
+        <v>0.744</v>
       </c>
       <c r="R21" t="n">
         <v>11.5</v>
@@ -4170,13 +4237,13 @@
         <v>42.2</v>
       </c>
       <c r="U21" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="V21" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="W21" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="X21" t="n">
         <v>4.2</v>
@@ -4185,19 +4252,19 @@
         <v>5</v>
       </c>
       <c r="Z21" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AA21" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AB21" t="n">
-        <v>97.59999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AD21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE21" t="n">
         <v>14</v>
@@ -4218,7 +4285,7 @@
         <v>20</v>
       </c>
       <c r="AK21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL21" t="n">
         <v>7</v>
@@ -4227,13 +4294,13 @@
         <v>2</v>
       </c>
       <c r="AN21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO21" t="n">
         <v>7</v>
       </c>
       <c r="AP21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AQ21" t="n">
         <v>20</v>
@@ -4263,16 +4330,16 @@
         <v>18</v>
       </c>
       <c r="AZ21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA21" t="n">
         <v>2</v>
       </c>
       <c r="BB21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-18-2011-12</t>
+          <t>2012-04-18</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E22" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F22" t="n">
         <v>17</v>
       </c>
       <c r="G22" t="n">
-        <v>0.726</v>
+        <v>0.721</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
@@ -4331,16 +4398,16 @@
         <v>20</v>
       </c>
       <c r="N22" t="n">
-        <v>0.357</v>
+        <v>0.356</v>
       </c>
       <c r="O22" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="P22" t="n">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.802</v>
+        <v>0.799</v>
       </c>
       <c r="R22" t="n">
         <v>11</v>
@@ -4355,7 +4422,7 @@
         <v>18.4</v>
       </c>
       <c r="V22" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="W22" t="n">
         <v>7.6</v>
@@ -4367,19 +4434,19 @@
         <v>4.7</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AA22" t="n">
         <v>20.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>102.8</v>
+        <v>102.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4406,10 +4473,10 @@
         <v>11</v>
       </c>
       <c r="AM22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO22" t="n">
         <v>1</v>
@@ -4436,7 +4503,7 @@
         <v>30</v>
       </c>
       <c r="AW22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX22" t="n">
         <v>1</v>
@@ -4445,10 +4512,10 @@
         <v>11</v>
       </c>
       <c r="AZ22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB22" t="n">
         <v>2</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-18-2011-12</t>
+          <t>2012-04-18</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E23" t="n">
         <v>36</v>
       </c>
       <c r="F23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G23" t="n">
-        <v>0.581</v>
+        <v>0.59</v>
       </c>
       <c r="H23" t="n">
         <v>48.3</v>
@@ -4507,28 +4574,28 @@
         <v>0.443</v>
       </c>
       <c r="L23" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="M23" t="n">
         <v>26.8</v>
       </c>
       <c r="N23" t="n">
-        <v>0.378</v>
+        <v>0.38</v>
       </c>
       <c r="O23" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="P23" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="Q23" t="n">
         <v>0.658</v>
       </c>
       <c r="R23" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="S23" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="T23" t="n">
         <v>42.7</v>
@@ -4543,34 +4610,34 @@
         <v>6.8</v>
       </c>
       <c r="X23" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y23" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z23" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="AA23" t="n">
         <v>19.9</v>
       </c>
       <c r="AB23" t="n">
-        <v>94.5</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE23" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AF23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG23" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AH23" t="n">
         <v>15</v>
@@ -4579,10 +4646,10 @@
         <v>26</v>
       </c>
       <c r="AJ23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL23" t="n">
         <v>1</v>
@@ -4591,25 +4658,25 @@
         <v>1</v>
       </c>
       <c r="AN23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO23" t="n">
         <v>28</v>
       </c>
       <c r="AP23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ23" t="n">
         <v>30</v>
       </c>
       <c r="AR23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AT23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU23" t="n">
         <v>21</v>
@@ -4618,25 +4685,25 @@
         <v>19</v>
       </c>
       <c r="AW23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ23" t="n">
         <v>4</v>
       </c>
       <c r="BA23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB23" t="n">
         <v>21</v>
       </c>
       <c r="BC23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-18-2011-12</t>
+          <t>2012-04-18</t>
         </is>
       </c>
     </row>
@@ -4665,43 +4732,43 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E24" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F24" t="n">
         <v>30</v>
       </c>
       <c r="G24" t="n">
-        <v>0.516</v>
+        <v>0.508</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
       </c>
       <c r="I24" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J24" t="n">
         <v>83.2</v>
       </c>
       <c r="K24" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="L24" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="M24" t="n">
         <v>14.5</v>
       </c>
       <c r="N24" t="n">
-        <v>0.364</v>
+        <v>0.36</v>
       </c>
       <c r="O24" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="P24" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="Q24" t="n">
         <v>0.741</v>
@@ -4710,16 +4777,16 @@
         <v>10.4</v>
       </c>
       <c r="S24" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="T24" t="n">
-        <v>43.1</v>
+        <v>43</v>
       </c>
       <c r="U24" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="V24" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="W24" t="n">
         <v>8</v>
@@ -4728,31 +4795,31 @@
         <v>5.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="AA24" t="n">
-        <v>16.1</v>
+        <v>16.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>93.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE24" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AF24" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AG24" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AH24" t="n">
         <v>26</v>
@@ -4773,7 +4840,7 @@
         <v>25</v>
       </c>
       <c r="AN24" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4788,19 +4855,19 @@
         <v>23</v>
       </c>
       <c r="AS24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV24" t="n">
         <v>1</v>
       </c>
       <c r="AW24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX24" t="n">
         <v>14</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-18-2011-12</t>
+          <t>2012-04-18</t>
         </is>
       </c>
     </row>
@@ -4847,28 +4914,28 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E25" t="n">
         <v>32</v>
       </c>
       <c r="F25" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G25" t="n">
-        <v>0.516</v>
+        <v>0.525</v>
       </c>
       <c r="H25" t="n">
         <v>48</v>
       </c>
       <c r="I25" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="J25" t="n">
         <v>82.2</v>
       </c>
       <c r="K25" t="n">
-        <v>0.459</v>
+        <v>0.46</v>
       </c>
       <c r="L25" t="n">
         <v>6.7</v>
@@ -4877,16 +4944,16 @@
         <v>19.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0.342</v>
+        <v>0.343</v>
       </c>
       <c r="O25" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="P25" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.759</v>
+        <v>0.76</v>
       </c>
       <c r="R25" t="n">
         <v>10.8</v>
@@ -4898,13 +4965,13 @@
         <v>41.6</v>
       </c>
       <c r="U25" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="V25" t="n">
         <v>14</v>
       </c>
       <c r="W25" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="X25" t="n">
         <v>5.6</v>
@@ -4916,31 +4983,31 @@
         <v>18.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AB25" t="n">
         <v>98.40000000000001</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE25" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AF25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG25" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH25" t="n">
         <v>30</v>
       </c>
       <c r="AI25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ25" t="n">
         <v>12</v>
@@ -4955,13 +5022,13 @@
         <v>16</v>
       </c>
       <c r="AN25" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AO25" t="n">
         <v>18</v>
       </c>
       <c r="AP25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ25" t="n">
         <v>14</v>
@@ -4970,16 +5037,16 @@
         <v>21</v>
       </c>
       <c r="AS25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU25" t="n">
         <v>6</v>
       </c>
       <c r="AV25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW25" t="n">
         <v>27</v>
@@ -4991,13 +5058,13 @@
         <v>4</v>
       </c>
       <c r="AZ25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA25" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BB25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC25" t="n">
         <v>19</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-18-2011-12</t>
+          <t>2012-04-18</t>
         </is>
       </c>
     </row>
@@ -5029,28 +5096,28 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E26" t="n">
         <v>28</v>
       </c>
       <c r="F26" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G26" t="n">
-        <v>0.444</v>
+        <v>0.452</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="J26" t="n">
         <v>82</v>
       </c>
       <c r="K26" t="n">
-        <v>0.445</v>
+        <v>0.446</v>
       </c>
       <c r="L26" t="n">
         <v>7.3</v>
@@ -5059,13 +5126,13 @@
         <v>20.9</v>
       </c>
       <c r="N26" t="n">
-        <v>0.349</v>
+        <v>0.35</v>
       </c>
       <c r="O26" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="P26" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="Q26" t="n">
         <v>0.795</v>
@@ -5074,7 +5141,7 @@
         <v>11.1</v>
       </c>
       <c r="S26" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="T26" t="n">
         <v>40.7</v>
@@ -5083,7 +5150,7 @@
         <v>20.5</v>
       </c>
       <c r="V26" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="W26" t="n">
         <v>8</v>
@@ -5101,13 +5168,13 @@
         <v>19.9</v>
       </c>
       <c r="AB26" t="n">
-        <v>97.5</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE26" t="n">
         <v>20</v>
@@ -5119,7 +5186,7 @@
         <v>20</v>
       </c>
       <c r="AH26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI26" t="n">
         <v>16</v>
@@ -5128,7 +5195,7 @@
         <v>14</v>
       </c>
       <c r="AK26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL26" t="n">
         <v>8</v>
@@ -5137,7 +5204,7 @@
         <v>9</v>
       </c>
       <c r="AN26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO26" t="n">
         <v>12</v>
@@ -5161,10 +5228,10 @@
         <v>17</v>
       </c>
       <c r="AV26" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AW26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX26" t="n">
         <v>16</v>
@@ -5176,13 +5243,13 @@
         <v>10</v>
       </c>
       <c r="BA26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BB26" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BC26" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-18-2011-12</t>
+          <t>2012-04-18</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E27" t="n">
         <v>20</v>
       </c>
       <c r="F27" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G27" t="n">
-        <v>0.323</v>
+        <v>0.328</v>
       </c>
       <c r="H27" t="n">
         <v>48.2</v>
@@ -5229,7 +5296,7 @@
         <v>37.3</v>
       </c>
       <c r="J27" t="n">
-        <v>86.40000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="K27" t="n">
         <v>0.432</v>
@@ -5244,28 +5311,28 @@
         <v>0.316</v>
       </c>
       <c r="O27" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="P27" t="n">
         <v>23.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.737</v>
+        <v>0.738</v>
       </c>
       <c r="R27" t="n">
         <v>13.5</v>
       </c>
       <c r="S27" t="n">
-        <v>29.5</v>
+        <v>29.7</v>
       </c>
       <c r="T27" t="n">
-        <v>43</v>
+        <v>43.1</v>
       </c>
       <c r="U27" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="V27" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W27" t="n">
         <v>8.5</v>
@@ -5274,22 +5341,22 @@
         <v>4.8</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="Z27" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AA27" t="n">
         <v>20.1</v>
       </c>
       <c r="AB27" t="n">
-        <v>98.2</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AC27" t="n">
-        <v>-6.4</v>
+        <v>-6.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE27" t="n">
         <v>26</v>
@@ -5319,7 +5386,7 @@
         <v>11</v>
       </c>
       <c r="AN27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO27" t="n">
         <v>11</v>
@@ -5328,16 +5395,16 @@
         <v>10</v>
       </c>
       <c r="AQ27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR27" t="n">
         <v>2</v>
       </c>
       <c r="AS27" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AT27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU27" t="n">
         <v>26</v>
@@ -5349,22 +5416,22 @@
         <v>5</v>
       </c>
       <c r="AX27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY27" t="n">
         <v>29</v>
       </c>
       <c r="AZ27" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA27" t="n">
         <v>11</v>
       </c>
       <c r="BB27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-18-2011-12</t>
+          <t>2012-04-18</t>
         </is>
       </c>
     </row>
@@ -5393,28 +5460,28 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E28" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F28" t="n">
         <v>16</v>
       </c>
       <c r="G28" t="n">
-        <v>0.738</v>
+        <v>0.733</v>
       </c>
       <c r="H28" t="n">
         <v>48.3</v>
       </c>
       <c r="I28" t="n">
-        <v>39.2</v>
+        <v>39.1</v>
       </c>
       <c r="J28" t="n">
         <v>82.7</v>
       </c>
       <c r="K28" t="n">
-        <v>0.474</v>
+        <v>0.472</v>
       </c>
       <c r="L28" t="n">
         <v>8.300000000000001</v>
@@ -5426,13 +5493,13 @@
         <v>0.39</v>
       </c>
       <c r="O28" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="P28" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.741</v>
+        <v>0.74</v>
       </c>
       <c r="R28" t="n">
         <v>10.3</v>
@@ -5444,7 +5511,7 @@
         <v>42.7</v>
       </c>
       <c r="U28" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="V28" t="n">
         <v>13.5</v>
@@ -5459,16 +5526,16 @@
         <v>5</v>
       </c>
       <c r="Z28" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="AA28" t="n">
         <v>19</v>
       </c>
       <c r="AB28" t="n">
-        <v>102.7</v>
+        <v>102.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="AD28" t="n">
         <v>25</v>
@@ -5501,13 +5568,13 @@
         <v>7</v>
       </c>
       <c r="AN28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO28" t="n">
         <v>19</v>
       </c>
       <c r="AP28" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AQ28" t="n">
         <v>22</v>
@@ -5516,7 +5583,7 @@
         <v>25</v>
       </c>
       <c r="AS28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-18-2011-12</t>
+          <t>2012-04-18</t>
         </is>
       </c>
     </row>
@@ -5575,58 +5642,58 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E29" t="n">
         <v>22</v>
       </c>
       <c r="F29" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G29" t="n">
-        <v>0.349</v>
+        <v>0.355</v>
       </c>
       <c r="H29" t="n">
         <v>48.4</v>
       </c>
       <c r="I29" t="n">
-        <v>34.4</v>
+        <v>34.5</v>
       </c>
       <c r="J29" t="n">
-        <v>78</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>0.441</v>
+        <v>0.442</v>
       </c>
       <c r="L29" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="M29" t="n">
         <v>16.3</v>
       </c>
       <c r="N29" t="n">
-        <v>0.337</v>
+        <v>0.342</v>
       </c>
       <c r="O29" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="P29" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.77</v>
+        <v>0.771</v>
       </c>
       <c r="R29" t="n">
         <v>10.5</v>
       </c>
       <c r="S29" t="n">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
       <c r="T29" t="n">
-        <v>41.6</v>
+        <v>41.7</v>
       </c>
       <c r="U29" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V29" t="n">
         <v>15</v>
@@ -5641,19 +5708,19 @@
         <v>4.9</v>
       </c>
       <c r="Z29" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="AA29" t="n">
         <v>18.6</v>
       </c>
       <c r="AB29" t="n">
-        <v>90.90000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="AC29" t="n">
-        <v>-3.8</v>
+        <v>-3.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE29" t="n">
         <v>23</v>
@@ -5665,13 +5732,13 @@
         <v>24</v>
       </c>
       <c r="AH29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI29" t="n">
         <v>27</v>
       </c>
       <c r="AJ29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK29" t="n">
         <v>21</v>
@@ -5683,31 +5750,31 @@
         <v>21</v>
       </c>
       <c r="AN29" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO29" t="n">
         <v>15</v>
       </c>
       <c r="AP29" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AQ29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR29" t="n">
         <v>22</v>
       </c>
       <c r="AS29" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AT29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU29" t="n">
         <v>15</v>
       </c>
       <c r="AV29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW29" t="n">
         <v>28</v>
@@ -5722,7 +5789,7 @@
         <v>30</v>
       </c>
       <c r="BA29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB29" t="n">
         <v>27</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-18-2011-12</t>
+          <t>2012-04-18</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E30" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F30" t="n">
         <v>30</v>
       </c>
       <c r="G30" t="n">
-        <v>0.524</v>
+        <v>0.516</v>
       </c>
       <c r="H30" t="n">
         <v>49</v>
@@ -5775,40 +5842,40 @@
         <v>38.2</v>
       </c>
       <c r="J30" t="n">
-        <v>83.7</v>
+        <v>83.8</v>
       </c>
       <c r="K30" t="n">
         <v>0.456</v>
       </c>
       <c r="L30" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="M30" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="N30" t="n">
-        <v>0.322</v>
+        <v>0.316</v>
       </c>
       <c r="O30" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="P30" t="n">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.753</v>
+        <v>0.752</v>
       </c>
       <c r="R30" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="S30" t="n">
-        <v>30.9</v>
+        <v>30.8</v>
       </c>
       <c r="T30" t="n">
         <v>43.9</v>
       </c>
       <c r="U30" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="V30" t="n">
         <v>14.3</v>
@@ -5823,28 +5890,28 @@
         <v>5.8</v>
       </c>
       <c r="Z30" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AA30" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB30" t="n">
-        <v>99.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE30" t="n">
         <v>14</v>
       </c>
       <c r="AF30" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AG30" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AH30" t="n">
         <v>2</v>
@@ -5859,19 +5926,19 @@
         <v>9</v>
       </c>
       <c r="AL30" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AM30" t="n">
         <v>29</v>
       </c>
       <c r="AN30" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO30" t="n">
         <v>6</v>
       </c>
       <c r="AP30" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AQ30" t="n">
         <v>18</v>
@@ -5880,19 +5947,19 @@
         <v>3</v>
       </c>
       <c r="AS30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV30" t="n">
         <v>13</v>
       </c>
       <c r="AW30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX30" t="n">
         <v>4</v>
@@ -5910,7 +5977,7 @@
         <v>6</v>
       </c>
       <c r="BC30" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-18-2011-12</t>
+          <t>2012-04-18</t>
         </is>
       </c>
     </row>
@@ -5939,64 +6006,64 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F31" t="n">
         <v>46</v>
       </c>
       <c r="G31" t="n">
-        <v>0.258</v>
+        <v>0.246</v>
       </c>
       <c r="H31" t="n">
         <v>48.1</v>
       </c>
       <c r="I31" t="n">
-        <v>36.3</v>
+        <v>36.1</v>
       </c>
       <c r="J31" t="n">
-        <v>82.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="K31" t="n">
-        <v>0.438</v>
+        <v>0.436</v>
       </c>
       <c r="L31" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="M31" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="N31" t="n">
-        <v>0.322</v>
+        <v>0.319</v>
       </c>
       <c r="O31" t="n">
         <v>15.6</v>
       </c>
       <c r="P31" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.73</v>
+        <v>0.732</v>
       </c>
       <c r="R31" t="n">
         <v>11.8</v>
       </c>
       <c r="S31" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="T31" t="n">
         <v>41.5</v>
       </c>
       <c r="U31" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="V31" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W31" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="X31" t="n">
         <v>6.5</v>
@@ -6005,19 +6072,19 @@
         <v>4.6</v>
       </c>
       <c r="Z31" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AA31" t="n">
         <v>18.8</v>
       </c>
       <c r="AB31" t="n">
-        <v>93.40000000000001</v>
+        <v>93</v>
       </c>
       <c r="AC31" t="n">
-        <v>-6.3</v>
+        <v>-6.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
@@ -6041,7 +6108,7 @@
         <v>25</v>
       </c>
       <c r="AL31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM31" t="n">
         <v>20</v>
@@ -6050,16 +6117,16 @@
         <v>27</v>
       </c>
       <c r="AO31" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AP31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ31" t="n">
         <v>26</v>
       </c>
       <c r="AR31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS31" t="n">
         <v>20</v>
@@ -6071,7 +6138,7 @@
         <v>27</v>
       </c>
       <c r="AV31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW31" t="n">
         <v>15</v>
@@ -6080,7 +6147,7 @@
         <v>2</v>
       </c>
       <c r="AY31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ31" t="n">
         <v>25</v>
@@ -6089,10 +6156,10 @@
         <v>22</v>
       </c>
       <c r="BB31" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BC31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-18-2011-12</t>
+          <t>2012-04-18</t>
         </is>
       </c>
     </row>
